--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$192</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7504" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7205" uniqueCount="704">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1791,234 +1791,210 @@
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
+    <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>Observation.component.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Why the component result is missing</t>
+  </si>
+  <si>
+    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
+  </si>
+  <si>
+    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
+  </si>
+  <si>
+    <t>Observation.component.interpretation</t>
+  </si>
+  <si>
+    <t>High, low, normal, etc.</t>
+  </si>
+  <si>
+    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>Observation.component.referenceRange</t>
+  </si>
+  <si>
+    <t>Provides guide for interpretation of component result</t>
+  </si>
+  <si>
+    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted</t>
+  </si>
+  <si>
+    <t>predicted</t>
+  </si>
+  <si>
+    <t>Vorhersage</t>
+  </si>
+  <si>
+    <t>vorhergesagtes Messergebnis</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.id</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.system</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.version</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.code</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.display</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:sct.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.id</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.system</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.version</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.code</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.display</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.coding:loinc.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code.text</t>
+  </si>
+  <si>
+    <t>Observation.component.code.text</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.value[x]</t>
+  </si>
+  <si>
     <t xml:space="preserve">type:$this}
 </t>
   </si>
   <si>
-    <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity</t>
   </si>
   <si>
     <t>valueQuantity</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.id</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.id</t>
   </si>
   <si>
     <t>Observation.component.value[x].id</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.extension</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.extension</t>
   </si>
   <si>
     <t>Observation.component.value[x].extension</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.value</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.value</t>
   </si>
   <si>
     <t>Observation.component.value[x].value</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.comparator</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.comparator</t>
   </si>
   <si>
     <t>Observation.component.value[x].comparator</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.unit</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.unit</t>
   </si>
   <si>
     <t>Observation.component.value[x].unit</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.system</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.system</t>
   </si>
   <si>
     <t>Observation.component.value[x].system</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.code</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.code</t>
   </si>
   <si>
     <t>Observation.component.value[x].code</t>
-  </si>
-  <si>
-    <t>Observation.component.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Why the component result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
-  </si>
-  <si>
-    <t>Observation.component.interpretation</t>
-  </si>
-  <si>
-    <t>High, low, normal, etc.</t>
-  </si>
-  <si>
-    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
-  </si>
-  <si>
-    <t>Observation.component.referenceRange</t>
-  </si>
-  <si>
-    <t>Provides guide for interpretation of component result</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted</t>
-  </si>
-  <si>
-    <t>predicted</t>
-  </si>
-  <si>
-    <t>Vorhersage</t>
-  </si>
-  <si>
-    <t>vorhergesagtes Messergebnis</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.id</t>
-  </si>
-  <si>
-    <t>Observation.component.code.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.id</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.system</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.version</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.code</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.display</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.system</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.version</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.code</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.display</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.text</t>
-  </si>
-  <si>
-    <t>Observation.component.code.text</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.value</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.unit</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.system</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.code</t>
   </si>
   <si>
     <t>Observation.component:predicted.dataAbsentReason</t>
@@ -2544,7 +2520,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO200"/>
+  <dimension ref="A1:AO192"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.09765625" customWidth="true" bestFit="true"/>
@@ -13593,14 +13569,16 @@
         <v>81</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AC94" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>563</v>
@@ -13621,7 +13599,7 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>389</v>
@@ -13635,14 +13613,12 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13660,22 +13636,22 @@
         <v>81</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>382</v>
+        <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13700,13 +13676,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13724,7 +13700,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13733,7 +13709,7 @@
         <v>91</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>103</v>
@@ -13742,35 +13718,35 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>389</v>
+        <v>438</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>573</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>81</v>
@@ -13782,16 +13758,20 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>106</v>
+        <v>574</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13815,13 +13795,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>81</v>
+        <v>446</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13839,46 +13819,46 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>108</v>
+        <v>573</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13897,18 +13877,20 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>112</v>
+        <v>577</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>113</v>
+        <v>578</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
       </c>
@@ -13944,19 +13926,19 @@
         <v>81</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>118</v>
+        <v>576</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13968,7 +13950,7 @@
         <v>81</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>81</v>
@@ -13977,7 +13959,7 @@
         <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>
@@ -13988,12 +13970,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>81</v>
       </c>
@@ -14014,19 +13998,19 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>394</v>
+        <v>491</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>395</v>
+        <v>581</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>396</v>
+        <v>582</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>397</v>
+        <v>552</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>398</v>
+        <v>553</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -14075,13 +14059,13 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>81</v>
@@ -14096,7 +14080,7 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>400</v>
+        <v>554</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
@@ -14107,10 +14091,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14127,30 +14111,26 @@
         <v>81</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>402</v>
+        <v>106</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>403</v>
+        <v>107</v>
       </c>
       <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>404</v>
-      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q99" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
         <v>81</v>
       </c>
@@ -14170,13 +14150,13 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -14194,7 +14174,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>408</v>
+        <v>108</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14206,7 +14186,7 @@
         <v>81</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>81</v>
@@ -14215,7 +14195,7 @@
         <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>81</v>
@@ -14224,46 +14204,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>411</v>
+        <v>112</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>81</v>
       </c>
@@ -14311,19 +14291,19 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>415</v>
+        <v>118</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>81</v>
@@ -14332,7 +14312,7 @@
         <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>81</v>
@@ -14341,45 +14321,47 @@
         <v>81</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I101" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>418</v>
+        <v>502</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O101" t="s" s="2">
-        <v>420</v>
+        <v>194</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -14428,19 +14410,19 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>422</v>
+        <v>504</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>81</v>
@@ -14449,7 +14431,7 @@
         <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>81</v>
@@ -14458,12 +14440,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>585</v>
+        <v>558</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14471,13 +14453,13 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>81</v>
@@ -14486,19 +14468,19 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>425</v>
+        <v>559</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>426</v>
+        <v>560</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>427</v>
+        <v>561</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>428</v>
+        <v>261</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14523,13 +14505,13 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14547,10 +14529,10 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>429</v>
+        <v>558</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>91</v>
@@ -14565,13 +14547,13 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>81</v>
+        <v>562</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>416</v>
+        <v>266</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14579,10 +14561,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14605,20 +14587,16 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>587</v>
+        <v>106</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>81</v>
       </c>
@@ -14642,13 +14620,13 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -14666,7 +14644,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>586</v>
+        <v>108</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14675,10 +14653,10 @@
         <v>91</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>81</v>
@@ -14687,7 +14665,7 @@
         <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>81</v>
@@ -14698,14 +14676,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>590</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>440</v>
+        <v>110</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14724,20 +14702,18 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>591</v>
+        <v>112</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>592</v>
+        <v>113</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>81</v>
       </c>
@@ -14761,31 +14737,31 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>590</v>
+        <v>118</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14797,30 +14773,30 @@
         <v>81</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14840,22 +14816,22 @@
         <v>81</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>594</v>
+        <v>243</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>595</v>
+        <v>244</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>494</v>
+        <v>245</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>495</v>
+        <v>246</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -14892,19 +14868,17 @@
         <v>81</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC105" s="2"/>
       <c r="AD105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>593</v>
+        <v>248</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14925,7 +14899,7 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>497</v>
+        <v>249</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
@@ -14936,13 +14910,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>549</v>
+        <v>592</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>597</v>
+        <v>309</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>81</v>
@@ -14964,19 +14938,19 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>491</v>
+        <v>144</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>598</v>
+        <v>310</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>599</v>
+        <v>311</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>552</v>
+        <v>245</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>553</v>
+        <v>246</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -15025,7 +14999,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>549</v>
+        <v>248</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15046,7 +15020,7 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>554</v>
+        <v>249</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>81</v>
@@ -15057,10 +15031,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>555</v>
+        <v>595</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15172,10 +15146,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15245,16 +15219,16 @@
         <v>81</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>118</v>
@@ -15289,45 +15263,45 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>501</v>
+        <v>81</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>502</v>
+        <v>276</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>503</v>
+        <v>277</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>114</v>
+        <v>278</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>194</v>
+        <v>279</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -15376,19 +15350,19 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>504</v>
+        <v>280</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>81</v>
@@ -15397,7 +15371,7 @@
         <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>81</v>
+        <v>281</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
@@ -15408,10 +15382,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>558</v>
+        <v>601</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15419,7 +15393,7 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>91</v>
@@ -15434,20 +15408,18 @@
         <v>92</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>559</v>
+        <v>283</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>560</v>
+        <v>284</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>81</v>
       </c>
@@ -15471,13 +15443,13 @@
         <v>81</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>81</v>
@@ -15495,10 +15467,10 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>558</v>
+        <v>286</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>91</v>
@@ -15513,13 +15485,13 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>562</v>
+        <v>81</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>81</v>
@@ -15527,10 +15499,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15550,19 +15522,21 @@
         <v>81</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>106</v>
+        <v>289</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>107</v>
+        <v>290</v>
       </c>
       <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
       </c>
@@ -15586,13 +15560,11 @@
         <v>81</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
@@ -15610,7 +15582,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>108</v>
+        <v>292</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15622,7 +15594,7 @@
         <v>81</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>81</v>
@@ -15631,7 +15603,7 @@
         <v>81</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>81</v>
@@ -15642,21 +15614,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>81</v>
@@ -15665,21 +15637,21 @@
         <v>81</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>112</v>
+        <v>295</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O112" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
       </c>
@@ -15715,31 +15687,31 @@
         <v>81</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>118</v>
+        <v>298</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>81</v>
@@ -15748,7 +15720,7 @@
         <v>81</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>81</v>
@@ -15759,10 +15731,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15773,7 +15745,7 @@
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>81</v>
@@ -15785,19 +15757,19 @@
         <v>92</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>144</v>
+        <v>301</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15834,23 +15806,25 @@
         <v>81</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC113" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>248</v>
+        <v>306</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>81</v>
@@ -15865,7 +15839,7 @@
         <v>81</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>249</v>
+        <v>307</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
@@ -15876,13 +15850,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>81</v>
@@ -15907,10 +15881,10 @@
         <v>144</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>245</v>
@@ -15997,10 +15971,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16112,10 +16086,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16229,10 +16203,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16348,10 +16322,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16465,10 +16439,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16530,7 +16504,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>81</v>
@@ -16580,10 +16554,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16697,10 +16671,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16814,16 +16788,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>81</v>
       </c>
@@ -16835,7 +16807,7 @@
         <v>91</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>81</v>
@@ -16844,19 +16816,19 @@
         <v>92</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>322</v>
+        <v>251</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -16905,13 +16877,13 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>81</v>
@@ -16926,7 +16898,7 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
@@ -16937,10 +16909,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>612</v>
+        <v>563</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16960,19 +16932,23 @@
         <v>81</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>105</v>
+        <v>564</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>106</v>
+        <v>565</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
       </c>
@@ -17008,19 +16984,17 @@
         <v>81</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="AC123" s="2"/>
       <c r="AD123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>108</v>
+        <v>563</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17032,41 +17006,43 @@
         <v>81</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C124" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>621</v>
+      </c>
       <c r="D124" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>81</v>
@@ -17075,21 +17051,23 @@
         <v>81</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>112</v>
+        <v>565</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>113</v>
+        <v>566</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O124" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
       </c>
@@ -17125,54 +17103,54 @@
         <v>81</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>118</v>
+        <v>563</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17192,23 +17170,19 @@
         <v>81</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>276</v>
+        <v>106</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>81</v>
       </c>
@@ -17256,7 +17230,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>280</v>
+        <v>108</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17268,7 +17242,7 @@
         <v>81</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>81</v>
@@ -17277,7 +17251,7 @@
         <v>81</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>281</v>
+        <v>81</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>81</v>
@@ -17288,21 +17262,21 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>81</v>
@@ -17311,19 +17285,19 @@
         <v>81</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>283</v>
+        <v>112</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>284</v>
+        <v>113</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>285</v>
+        <v>114</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17361,31 +17335,31 @@
         <v>81</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>286</v>
+        <v>118</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>81</v>
@@ -17394,7 +17368,7 @@
         <v>81</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>287</v>
+        <v>81</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
@@ -17403,12 +17377,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17422,7 +17396,7 @@
         <v>91</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>81</v>
@@ -17431,17 +17405,19 @@
         <v>92</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>166</v>
+        <v>394</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>289</v>
+        <v>395</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N127" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O127" t="s" s="2">
-        <v>291</v>
+        <v>398</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -17466,11 +17442,13 @@
         <v>81</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y127" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z127" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>81</v>
@@ -17488,7 +17466,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>292</v>
+        <v>399</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17509,7 +17487,7 @@
         <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>293</v>
+        <v>400</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>81</v>
@@ -17520,10 +17498,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17540,28 +17518,30 @@
         <v>81</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J128" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>295</v>
+        <v>402</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>296</v>
+        <v>403</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>297</v>
+        <v>404</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q128" s="2"/>
+      <c r="Q128" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="R128" t="s" s="2">
         <v>81</v>
       </c>
@@ -17581,13 +17561,13 @@
         <v>81</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>81</v>
@@ -17605,7 +17585,7 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>298</v>
+        <v>408</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17626,7 +17606,7 @@
         <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>299</v>
+        <v>409</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>81</v>
@@ -17635,12 +17615,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17654,7 +17634,7 @@
         <v>91</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>81</v>
@@ -17663,19 +17643,17 @@
         <v>92</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>301</v>
+        <v>105</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>302</v>
+        <v>411</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>305</v>
+        <v>413</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>81</v>
@@ -17685,7 +17663,7 @@
         <v>81</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>81</v>
@@ -17724,7 +17702,7 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>306</v>
+        <v>415</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17745,7 +17723,7 @@
         <v>81</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>307</v>
+        <v>416</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>
@@ -17754,12 +17732,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17773,7 +17751,7 @@
         <v>91</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>81</v>
@@ -17782,19 +17760,17 @@
         <v>92</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>251</v>
+        <v>418</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>254</v>
+        <v>420</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>81</v>
@@ -17804,7 +17780,7 @@
         <v>81</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>81</v>
@@ -17843,7 +17819,7 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17852,7 +17828,7 @@
         <v>91</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>103</v>
@@ -17864,7 +17840,7 @@
         <v>81</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>256</v>
+        <v>416</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>81</v>
@@ -17873,12 +17849,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="131" hidden="true">
+    <row r="131">
       <c r="A131" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B131" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17892,7 +17868,7 @@
         <v>91</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>81</v>
@@ -17901,19 +17877,19 @@
         <v>92</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>564</v>
+        <v>166</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>565</v>
+        <v>425</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>566</v>
+        <v>426</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>567</v>
+        <v>427</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>386</v>
+        <v>428</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
@@ -17923,7 +17899,7 @@
         <v>81</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>81</v>
@@ -17950,17 +17926,19 @@
         <v>81</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AC131" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>563</v>
+        <v>429</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17978,16 +17956,16 @@
         <v>81</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132" hidden="true">
@@ -17995,11 +17973,9 @@
         <v>636</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C132" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>81</v>
       </c>
@@ -18017,22 +17993,22 @@
         <v>81</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>382</v>
+        <v>232</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
@@ -18057,13 +18033,13 @@
         <v>81</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>81</v>
@@ -18081,7 +18057,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18090,7 +18066,7 @@
         <v>91</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>103</v>
@@ -18099,16 +18075,16 @@
         <v>81</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>389</v>
+        <v>438</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
     </row>
     <row r="133" hidden="true">
@@ -18120,14 +18096,14 @@
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>81</v>
@@ -18139,16 +18115,20 @@
         <v>81</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>106</v>
+        <v>574</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>81</v>
       </c>
@@ -18172,13 +18152,13 @@
         <v>81</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>81</v>
+        <v>446</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>81</v>
@@ -18196,34 +18176,34 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>108</v>
+        <v>573</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
     </row>
     <row r="134" hidden="true">
@@ -18231,11 +18211,11 @@
         <v>638</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18254,18 +18234,20 @@
         <v>81</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>112</v>
+        <v>577</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>113</v>
+        <v>578</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O134" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="P134" t="s" s="2">
         <v>81</v>
       </c>
@@ -18301,19 +18283,19 @@
         <v>81</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>118</v>
+        <v>576</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18325,7 +18307,7 @@
         <v>81</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>81</v>
@@ -18334,7 +18316,7 @@
         <v>81</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>81</v>
@@ -18343,14 +18325,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="135" hidden="true">
+    <row r="135">
       <c r="A135" t="s" s="2">
         <v>639</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C135" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>640</v>
+      </c>
       <c r="D135" t="s" s="2">
         <v>81</v>
       </c>
@@ -18362,7 +18346,7 @@
         <v>91</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>81</v>
@@ -18371,19 +18355,19 @@
         <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>394</v>
+        <v>491</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>395</v>
+        <v>641</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>396</v>
+        <v>642</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>397</v>
+        <v>552</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>398</v>
+        <v>553</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>81</v>
@@ -18432,13 +18416,13 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>81</v>
@@ -18453,7 +18437,7 @@
         <v>81</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>400</v>
+        <v>554</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -18464,10 +18448,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18484,30 +18468,26 @@
         <v>81</v>
       </c>
       <c r="I136" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>402</v>
+        <v>106</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>403</v>
+        <v>107</v>
       </c>
       <c r="N136" s="2"/>
-      <c r="O136" t="s" s="2">
-        <v>404</v>
-      </c>
+      <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q136" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="Q136" s="2"/>
       <c r="R136" t="s" s="2">
         <v>81</v>
       </c>
@@ -18527,13 +18507,13 @@
         <v>81</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>81</v>
@@ -18551,7 +18531,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>408</v>
+        <v>108</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18563,7 +18543,7 @@
         <v>81</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>81</v>
@@ -18572,7 +18552,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -18583,21 +18563,21 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>81</v>
@@ -18606,21 +18586,21 @@
         <v>81</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>411</v>
+        <v>112</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>81</v>
       </c>
@@ -18629,7 +18609,7 @@
         <v>81</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>81</v>
@@ -18668,19 +18648,19 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>415</v>
+        <v>118</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>81</v>
@@ -18689,7 +18669,7 @@
         <v>81</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>
@@ -18700,43 +18680,45 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J138" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>418</v>
+        <v>502</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N138" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O138" t="s" s="2">
-        <v>420</v>
+        <v>194</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>81</v>
@@ -18746,7 +18728,7 @@
         <v>81</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>81</v>
@@ -18785,19 +18767,19 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>422</v>
+        <v>504</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>81</v>
@@ -18806,7 +18788,7 @@
         <v>81</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>81</v>
@@ -18817,10 +18799,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>585</v>
+        <v>558</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18828,7 +18810,7 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>91</v>
@@ -18843,19 +18825,19 @@
         <v>92</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>425</v>
+        <v>559</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>426</v>
+        <v>560</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>427</v>
+        <v>561</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>428</v>
+        <v>261</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>81</v>
@@ -18865,7 +18847,7 @@
         <v>81</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>81</v>
@@ -18880,13 +18862,13 @@
         <v>81</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>81</v>
@@ -18904,10 +18886,10 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>429</v>
+        <v>558</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>91</v>
@@ -18922,13 +18904,13 @@
         <v>81</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>81</v>
+        <v>562</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>416</v>
+        <v>266</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>81</v>
@@ -18936,10 +18918,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18962,20 +18944,16 @@
         <v>81</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>587</v>
+        <v>106</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>81</v>
       </c>
@@ -18999,13 +18977,13 @@
         <v>81</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>81</v>
@@ -19023,7 +19001,7 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>586</v>
+        <v>108</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19032,10 +19010,10 @@
         <v>91</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>81</v>
@@ -19044,7 +19022,7 @@
         <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>81</v>
@@ -19055,14 +19033,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>590</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>440</v>
+        <v>110</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -19081,20 +19059,18 @@
         <v>81</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>591</v>
+        <v>112</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>592</v>
+        <v>113</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>81</v>
       </c>
@@ -19118,31 +19094,31 @@
         <v>81</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>590</v>
+        <v>118</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19154,30 +19130,30 @@
         <v>81</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19197,22 +19173,22 @@
         <v>81</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>594</v>
+        <v>243</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>595</v>
+        <v>244</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>494</v>
+        <v>245</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>495</v>
+        <v>246</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>81</v>
@@ -19249,19 +19225,17 @@
         <v>81</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC142" s="2"/>
       <c r="AD142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>593</v>
+        <v>248</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19282,7 +19256,7 @@
         <v>81</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>497</v>
+        <v>249</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>81</v>
@@ -19293,13 +19267,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>549</v>
+        <v>592</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>648</v>
+        <v>309</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>81</v>
@@ -19321,19 +19295,19 @@
         <v>92</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>491</v>
+        <v>144</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>649</v>
+        <v>310</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>650</v>
+        <v>311</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>552</v>
+        <v>245</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>553</v>
+        <v>246</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -19382,7 +19356,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>549</v>
+        <v>248</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19403,7 +19377,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>554</v>
+        <v>249</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -19417,7 +19391,7 @@
         <v>651</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>555</v>
+        <v>595</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19532,7 +19506,7 @@
         <v>652</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19602,16 +19576,16 @@
         <v>81</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF145" t="s" s="2">
         <v>118</v>
@@ -19649,42 +19623,42 @@
         <v>653</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>501</v>
+        <v>81</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I146" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J146" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>502</v>
+        <v>276</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>503</v>
+        <v>277</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>114</v>
+        <v>278</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>194</v>
+        <v>279</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>81</v>
@@ -19733,19 +19707,19 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>504</v>
+        <v>280</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>81</v>
@@ -19754,7 +19728,7 @@
         <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>81</v>
+        <v>281</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>81</v>
@@ -19768,7 +19742,7 @@
         <v>654</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>558</v>
+        <v>601</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19776,7 +19750,7 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G147" t="s" s="2">
         <v>91</v>
@@ -19791,20 +19765,18 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>559</v>
+        <v>283</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>560</v>
+        <v>284</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>81</v>
       </c>
@@ -19828,13 +19800,13 @@
         <v>81</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>81</v>
@@ -19852,10 +19824,10 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>558</v>
+        <v>286</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>91</v>
@@ -19870,13 +19842,13 @@
         <v>81</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>562</v>
+        <v>81</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>81</v>
@@ -19887,7 +19859,7 @@
         <v>655</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19907,19 +19879,21 @@
         <v>81</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>106</v>
+        <v>289</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>107</v>
+        <v>290</v>
       </c>
       <c r="N148" s="2"/>
-      <c r="O148" s="2"/>
+      <c r="O148" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>81</v>
       </c>
@@ -19943,13 +19917,11 @@
         <v>81</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>81</v>
@@ -19967,7 +19939,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>108</v>
+        <v>292</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19979,7 +19951,7 @@
         <v>81</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>81</v>
@@ -19988,7 +19960,7 @@
         <v>81</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>81</v>
@@ -20002,18 +19974,18 @@
         <v>656</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>81</v>
@@ -20022,21 +19994,21 @@
         <v>81</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>112</v>
+        <v>295</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O149" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N149" s="2"/>
+      <c r="O149" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P149" t="s" s="2">
         <v>81</v>
       </c>
@@ -20072,31 +20044,31 @@
         <v>81</v>
       </c>
       <c r="AB149" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC149" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE149" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>118</v>
+        <v>298</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>81</v>
@@ -20105,7 +20077,7 @@
         <v>81</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>81</v>
@@ -20119,7 +20091,7 @@
         <v>657</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20130,7 +20102,7 @@
         <v>79</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>81</v>
@@ -20142,19 +20114,19 @@
         <v>92</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>144</v>
+        <v>301</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>81</v>
@@ -20191,23 +20163,25 @@
         <v>81</v>
       </c>
       <c r="AB150" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC150" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>248</v>
+        <v>306</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>81</v>
@@ -20222,7 +20196,7 @@
         <v>81</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>249</v>
+        <v>307</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>81</v>
@@ -20236,10 +20210,10 @@
         <v>658</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>81</v>
@@ -20264,10 +20238,10 @@
         <v>144</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="N151" t="s" s="2">
         <v>245</v>
@@ -20357,7 +20331,7 @@
         <v>659</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20472,7 +20446,7 @@
         <v>660</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20589,7 +20563,7 @@
         <v>661</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20708,7 +20682,7 @@
         <v>662</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20825,7 +20799,7 @@
         <v>663</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20887,7 +20861,7 @@
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>81</v>
@@ -20940,7 +20914,7 @@
         <v>664</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21057,7 +21031,7 @@
         <v>665</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21171,16 +21145,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
         <v>666</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
         <v>81</v>
       </c>
@@ -21192,7 +21164,7 @@
         <v>91</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I159" t="s" s="2">
         <v>81</v>
@@ -21201,19 +21173,19 @@
         <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>322</v>
+        <v>251</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>81</v>
@@ -21262,13 +21234,13 @@
         <v>81</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>81</v>
@@ -21283,7 +21255,7 @@
         <v>81</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>81</v>
@@ -21297,7 +21269,7 @@
         <v>667</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>612</v>
+        <v>563</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21317,19 +21289,23 @@
         <v>81</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>105</v>
+        <v>564</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>106</v>
+        <v>565</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P160" t="s" s="2">
         <v>81</v>
       </c>
@@ -21365,19 +21341,17 @@
         <v>81</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="AC160" s="2"/>
       <c r="AD160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE160" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>108</v>
+        <v>563</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21389,22 +21363,22 @@
         <v>81</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
     </row>
     <row r="161" hidden="true">
@@ -21412,18 +21386,20 @@
         <v>668</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C161" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="C161" t="s" s="2">
+        <v>621</v>
+      </c>
       <c r="D161" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>81</v>
@@ -21432,21 +21408,23 @@
         <v>81</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>112</v>
+        <v>565</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>113</v>
+        <v>566</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O161" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="O161" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P161" t="s" s="2">
         <v>81</v>
       </c>
@@ -21482,46 +21460,46 @@
         <v>81</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>118</v>
+        <v>563</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
     </row>
     <row r="162" hidden="true">
@@ -21529,7 +21507,7 @@
         <v>669</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21549,23 +21527,19 @@
         <v>81</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>276</v>
+        <v>106</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N162" s="2"/>
+      <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>81</v>
       </c>
@@ -21613,7 +21587,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>280</v>
+        <v>108</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21625,7 +21599,7 @@
         <v>81</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>81</v>
@@ -21634,7 +21608,7 @@
         <v>81</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>281</v>
+        <v>81</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>81</v>
@@ -21648,18 +21622,18 @@
         <v>670</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>81</v>
@@ -21668,19 +21642,19 @@
         <v>81</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>283</v>
+        <v>112</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>284</v>
+        <v>113</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>285</v>
+        <v>114</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -21718,31 +21692,31 @@
         <v>81</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC163" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE163" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>286</v>
+        <v>118</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>81</v>
@@ -21751,7 +21725,7 @@
         <v>81</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>287</v>
+        <v>81</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>81</v>
@@ -21760,12 +21734,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="164" hidden="true">
+    <row r="164">
       <c r="A164" t="s" s="2">
         <v>671</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21779,7 +21753,7 @@
         <v>91</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>81</v>
@@ -21788,17 +21762,19 @@
         <v>92</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>166</v>
+        <v>394</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>289</v>
+        <v>395</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N164" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O164" t="s" s="2">
-        <v>291</v>
+        <v>398</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
@@ -21823,11 +21799,13 @@
         <v>81</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y164" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z164" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>81</v>
@@ -21845,7 +21823,7 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>292</v>
+        <v>399</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -21866,7 +21844,7 @@
         <v>81</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>293</v>
+        <v>400</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>81</v>
@@ -21880,7 +21858,7 @@
         <v>672</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21897,28 +21875,30 @@
         <v>81</v>
       </c>
       <c r="I165" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J165" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>295</v>
+        <v>402</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>296</v>
+        <v>403</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>297</v>
+        <v>404</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q165" s="2"/>
+      <c r="Q165" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="R165" t="s" s="2">
         <v>81</v>
       </c>
@@ -21938,13 +21918,13 @@
         <v>81</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>81</v>
@@ -21962,7 +21942,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>298</v>
+        <v>408</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -21983,7 +21963,7 @@
         <v>81</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>299</v>
+        <v>409</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>81</v>
@@ -21992,12 +21972,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
         <v>673</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22011,7 +21991,7 @@
         <v>91</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>81</v>
@@ -22020,19 +22000,17 @@
         <v>92</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>301</v>
+        <v>105</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>302</v>
+        <v>411</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>305</v>
+        <v>413</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>81</v>
@@ -22042,7 +22020,7 @@
         <v>81</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>81</v>
@@ -22081,7 +22059,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>306</v>
+        <v>415</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22102,7 +22080,7 @@
         <v>81</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>307</v>
+        <v>416</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>81</v>
@@ -22111,12 +22089,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="167" hidden="true">
+    <row r="167">
       <c r="A167" t="s" s="2">
         <v>674</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22130,7 +22108,7 @@
         <v>91</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>81</v>
@@ -22139,19 +22117,17 @@
         <v>92</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>251</v>
+        <v>418</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>254</v>
+        <v>420</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>81</v>
@@ -22161,7 +22137,7 @@
         <v>81</v>
       </c>
       <c r="S167" t="s" s="2">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="T167" t="s" s="2">
         <v>81</v>
@@ -22200,7 +22176,7 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22209,7 +22185,7 @@
         <v>91</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>103</v>
@@ -22221,7 +22197,7 @@
         <v>81</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>256</v>
+        <v>416</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>81</v>
@@ -22230,12 +22206,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="168" hidden="true">
+    <row r="168">
       <c r="A168" t="s" s="2">
         <v>675</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>563</v>
+        <v>635</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22249,7 +22225,7 @@
         <v>91</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>81</v>
@@ -22258,19 +22234,19 @@
         <v>92</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>564</v>
+        <v>166</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>565</v>
+        <v>425</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>566</v>
+        <v>426</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>567</v>
+        <v>427</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>386</v>
+        <v>428</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>81</v>
@@ -22280,7 +22256,7 @@
         <v>81</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>81</v>
@@ -22307,17 +22283,19 @@
         <v>81</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AC168" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD168" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>563</v>
+        <v>429</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22335,16 +22313,16 @@
         <v>81</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
     </row>
     <row r="169" hidden="true">
@@ -22352,11 +22330,9 @@
         <v>676</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
         <v>81</v>
       </c>
@@ -22374,22 +22350,22 @@
         <v>81</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>382</v>
+        <v>232</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>81</v>
@@ -22414,13 +22390,13 @@
         <v>81</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>81</v>
@@ -22438,7 +22414,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22447,7 +22423,7 @@
         <v>91</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>103</v>
@@ -22456,16 +22432,16 @@
         <v>81</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>389</v>
+        <v>438</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
     </row>
     <row r="170" hidden="true">
@@ -22477,14 +22453,14 @@
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>81</v>
@@ -22496,16 +22472,20 @@
         <v>81</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>106</v>
+        <v>574</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N170" s="2"/>
-      <c r="O170" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P170" t="s" s="2">
         <v>81</v>
       </c>
@@ -22529,13 +22509,13 @@
         <v>81</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>81</v>
+        <v>446</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>81</v>
@@ -22553,34 +22533,34 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>108</v>
+        <v>573</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
     </row>
     <row r="171" hidden="true">
@@ -22588,11 +22568,11 @@
         <v>678</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -22611,18 +22591,20 @@
         <v>81</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>112</v>
+        <v>577</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>113</v>
+        <v>578</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O171" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="P171" t="s" s="2">
         <v>81</v>
       </c>
@@ -22658,19 +22640,19 @@
         <v>81</v>
       </c>
       <c r="AB171" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC171" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE171" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>118</v>
+        <v>576</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -22682,7 +22664,7 @@
         <v>81</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>81</v>
@@ -22691,7 +22673,7 @@
         <v>81</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>81</v>
@@ -22700,14 +22682,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
         <v>679</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C172" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="C172" t="s" s="2">
+        <v>680</v>
+      </c>
       <c r="D172" t="s" s="2">
         <v>81</v>
       </c>
@@ -22719,7 +22703,7 @@
         <v>91</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>81</v>
@@ -22728,19 +22712,19 @@
         <v>92</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>394</v>
+        <v>491</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>395</v>
+        <v>681</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>396</v>
+        <v>682</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>397</v>
+        <v>552</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>398</v>
+        <v>553</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>81</v>
@@ -22789,13 +22773,13 @@
         <v>81</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>81</v>
@@ -22810,7 +22794,7 @@
         <v>81</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>400</v>
+        <v>554</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>81</v>
@@ -22821,10 +22805,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22841,30 +22825,26 @@
         <v>81</v>
       </c>
       <c r="I173" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>402</v>
+        <v>106</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>403</v>
+        <v>107</v>
       </c>
       <c r="N173" s="2"/>
-      <c r="O173" t="s" s="2">
-        <v>404</v>
-      </c>
+      <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q173" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="Q173" s="2"/>
       <c r="R173" t="s" s="2">
         <v>81</v>
       </c>
@@ -22884,13 +22864,13 @@
         <v>81</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>81</v>
@@ -22908,7 +22888,7 @@
         <v>81</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>408</v>
+        <v>108</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -22920,7 +22900,7 @@
         <v>81</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>81</v>
@@ -22929,7 +22909,7 @@
         <v>81</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>81</v>
@@ -22940,21 +22920,21 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>81</v>
@@ -22963,21 +22943,21 @@
         <v>81</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>411</v>
+        <v>112</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N174" s="2"/>
-      <c r="O174" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>81</v>
       </c>
@@ -22986,7 +22966,7 @@
         <v>81</v>
       </c>
       <c r="S174" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="T174" t="s" s="2">
         <v>81</v>
@@ -23025,19 +23005,19 @@
         <v>81</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>415</v>
+        <v>118</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>81</v>
@@ -23046,7 +23026,7 @@
         <v>81</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>81</v>
@@ -23057,43 +23037,45 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I175" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J175" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>418</v>
+        <v>502</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N175" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O175" t="s" s="2">
-        <v>420</v>
+        <v>194</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>81</v>
@@ -23103,7 +23085,7 @@
         <v>81</v>
       </c>
       <c r="S175" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="T175" t="s" s="2">
         <v>81</v>
@@ -23142,19 +23124,19 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>422</v>
+        <v>504</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>81</v>
@@ -23163,7 +23145,7 @@
         <v>81</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>81</v>
@@ -23174,10 +23156,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>585</v>
+        <v>558</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23185,7 +23167,7 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G176" t="s" s="2">
         <v>91</v>
@@ -23200,19 +23182,19 @@
         <v>92</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>425</v>
+        <v>559</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>426</v>
+        <v>560</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>427</v>
+        <v>561</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>428</v>
+        <v>261</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>81</v>
@@ -23222,7 +23204,7 @@
         <v>81</v>
       </c>
       <c r="S176" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="T176" t="s" s="2">
         <v>81</v>
@@ -23237,13 +23219,13 @@
         <v>81</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>81</v>
@@ -23261,10 +23243,10 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>429</v>
+        <v>558</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>91</v>
@@ -23279,13 +23261,13 @@
         <v>81</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>81</v>
+        <v>562</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>416</v>
+        <v>266</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>81</v>
@@ -23293,10 +23275,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23319,20 +23301,16 @@
         <v>81</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>587</v>
+        <v>106</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N177" s="2"/>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>81</v>
       </c>
@@ -23356,13 +23334,13 @@
         <v>81</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>81</v>
@@ -23380,7 +23358,7 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>586</v>
+        <v>108</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23389,10 +23367,10 @@
         <v>91</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>81</v>
@@ -23401,7 +23379,7 @@
         <v>81</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>81</v>
@@ -23412,14 +23390,14 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>590</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>440</v>
+        <v>110</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
@@ -23438,20 +23416,18 @@
         <v>81</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>591</v>
+        <v>112</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>592</v>
+        <v>113</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>81</v>
       </c>
@@ -23475,31 +23451,31 @@
         <v>81</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC178" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>590</v>
+        <v>118</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23511,30 +23487,30 @@
         <v>81</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23554,22 +23530,22 @@
         <v>81</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>594</v>
+        <v>243</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>595</v>
+        <v>244</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>494</v>
+        <v>245</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>495</v>
+        <v>246</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>81</v>
@@ -23606,19 +23582,17 @@
         <v>81</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC179" s="2"/>
       <c r="AD179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>593</v>
+        <v>248</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -23639,7 +23613,7 @@
         <v>81</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>497</v>
+        <v>249</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>81</v>
@@ -23650,13 +23624,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>549</v>
+        <v>592</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>688</v>
+        <v>309</v>
       </c>
       <c r="D180" t="s" s="2">
         <v>81</v>
@@ -23678,19 +23652,19 @@
         <v>92</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>491</v>
+        <v>144</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>689</v>
+        <v>310</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>690</v>
+        <v>311</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>552</v>
+        <v>245</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>553</v>
+        <v>246</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>81</v>
@@ -23700,7 +23674,7 @@
         <v>81</v>
       </c>
       <c r="S180" t="s" s="2">
-        <v>81</v>
+        <v>691</v>
       </c>
       <c r="T180" t="s" s="2">
         <v>81</v>
@@ -23739,7 +23713,7 @@
         <v>81</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>549</v>
+        <v>248</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
@@ -23760,7 +23734,7 @@
         <v>81</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>554</v>
+        <v>249</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>81</v>
@@ -23771,10 +23745,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>555</v>
+        <v>595</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23886,10 +23860,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23959,16 +23933,16 @@
         <v>81</v>
       </c>
       <c r="AB182" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC182" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE182" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF182" t="s" s="2">
         <v>118</v>
@@ -24003,45 +23977,45 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>501</v>
+        <v>81</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I183" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J183" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>502</v>
+        <v>276</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>503</v>
+        <v>277</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>114</v>
+        <v>278</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>194</v>
+        <v>279</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>81</v>
@@ -24090,19 +24064,19 @@
         <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>504</v>
+        <v>280</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>81</v>
@@ -24111,7 +24085,7 @@
         <v>81</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>81</v>
+        <v>281</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>81</v>
@@ -24122,10 +24096,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>558</v>
+        <v>601</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24133,7 +24107,7 @@
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
         <v>91</v>
@@ -24148,20 +24122,18 @@
         <v>92</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>559</v>
+        <v>283</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>560</v>
+        <v>284</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>81</v>
       </c>
@@ -24185,13 +24157,13 @@
         <v>81</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>81</v>
@@ -24209,10 +24181,10 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>558</v>
+        <v>286</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH184" t="s" s="2">
         <v>91</v>
@@ -24227,13 +24199,13 @@
         <v>81</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>562</v>
+        <v>81</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>81</v>
@@ -24241,10 +24213,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24264,19 +24236,21 @@
         <v>81</v>
       </c>
       <c r="J185" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>106</v>
+        <v>289</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>107</v>
+        <v>290</v>
       </c>
       <c r="N185" s="2"/>
-      <c r="O185" s="2"/>
+      <c r="O185" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P185" t="s" s="2">
         <v>81</v>
       </c>
@@ -24300,13 +24274,11 @@
         <v>81</v>
       </c>
       <c r="X185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y185" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y185" s="2"/>
       <c r="Z185" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>81</v>
@@ -24324,7 +24296,7 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>108</v>
+        <v>292</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -24336,7 +24308,7 @@
         <v>81</v>
       </c>
       <c r="AJ185" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK185" t="s" s="2">
         <v>81</v>
@@ -24345,7 +24317,7 @@
         <v>81</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>81</v>
@@ -24356,21 +24328,21 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>81</v>
@@ -24379,21 +24351,21 @@
         <v>81</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>112</v>
+        <v>295</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O186" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N186" s="2"/>
+      <c r="O186" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P186" t="s" s="2">
         <v>81</v>
       </c>
@@ -24429,31 +24401,31 @@
         <v>81</v>
       </c>
       <c r="AB186" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC186" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD186" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE186" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>118</v>
+        <v>298</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK186" t="s" s="2">
         <v>81</v>
@@ -24462,7 +24434,7 @@
         <v>81</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>81</v>
@@ -24473,10 +24445,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24487,7 +24459,7 @@
         <v>79</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>81</v>
@@ -24499,19 +24471,19 @@
         <v>92</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>144</v>
+        <v>301</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>81</v>
@@ -24548,23 +24520,25 @@
         <v>81</v>
       </c>
       <c r="AB187" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC187" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD187" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE187" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>248</v>
+        <v>306</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH187" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI187" t="s" s="2">
         <v>81</v>
@@ -24579,7 +24553,7 @@
         <v>81</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>249</v>
+        <v>307</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>81</v>
@@ -24588,16 +24562,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C188" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
         <v>81</v>
       </c>
@@ -24609,7 +24581,7 @@
         <v>91</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>81</v>
@@ -24618,19 +24590,19 @@
         <v>92</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>310</v>
+        <v>251</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>311</v>
+        <v>252</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>81</v>
@@ -24640,7 +24612,7 @@
         <v>81</v>
       </c>
       <c r="S188" t="s" s="2">
-        <v>699</v>
+        <v>81</v>
       </c>
       <c r="T188" t="s" s="2">
         <v>81</v>
@@ -24679,13 +24651,13 @@
         <v>81</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH188" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI188" t="s" s="2">
         <v>81</v>
@@ -24700,7 +24672,7 @@
         <v>81</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>81</v>
@@ -24714,7 +24686,7 @@
         <v>700</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>612</v>
+        <v>563</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24734,19 +24706,23 @@
         <v>81</v>
       </c>
       <c r="J189" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>105</v>
+        <v>564</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>106</v>
+        <v>565</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O189" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P189" t="s" s="2">
         <v>81</v>
       </c>
@@ -24794,7 +24770,7 @@
         <v>81</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>108</v>
+        <v>563</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -24806,22 +24782,22 @@
         <v>81</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AN189" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" hidden="true">
@@ -24829,18 +24805,18 @@
         <v>701</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>614</v>
+        <v>569</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H190" t="s" s="2">
         <v>81</v>
@@ -24852,18 +24828,20 @@
         <v>81</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>112</v>
+        <v>570</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>113</v>
+        <v>571</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O190" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P190" t="s" s="2">
         <v>81</v>
       </c>
@@ -24887,43 +24865,43 @@
         <v>81</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="Z190" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB190" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC190" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD190" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE190" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>118</v>
+        <v>569</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>81</v>
@@ -24932,7 +24910,7 @@
         <v>81</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AN190" t="s" s="2">
         <v>81</v>
@@ -24946,18 +24924,18 @@
         <v>702</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>616</v>
+        <v>573</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H191" t="s" s="2">
         <v>81</v>
@@ -24966,22 +24944,22 @@
         <v>81</v>
       </c>
       <c r="J191" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>276</v>
+        <v>574</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>277</v>
+        <v>575</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>278</v>
+        <v>443</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>279</v>
+        <v>444</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>81</v>
@@ -25006,13 +24984,13 @@
         <v>81</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="Z191" t="s" s="2">
-        <v>81</v>
+        <v>446</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>81</v>
@@ -25030,13 +25008,13 @@
         <v>81</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>280</v>
+        <v>573</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>81</v>
@@ -25048,16 +25026,16 @@
         <v>81</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>281</v>
+        <v>448</v>
       </c>
       <c r="AN191" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
     </row>
     <row r="192" hidden="true">
@@ -25065,7 +25043,7 @@
         <v>703</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>618</v>
+        <v>576</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25076,7 +25054,7 @@
         <v>79</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>81</v>
@@ -25085,21 +25063,23 @@
         <v>81</v>
       </c>
       <c r="J192" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>283</v>
+        <v>577</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>284</v>
+        <v>578</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O192" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="P192" t="s" s="2">
         <v>81</v>
       </c>
@@ -25147,13 +25127,13 @@
         <v>81</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>286</v>
+        <v>576</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI192" t="s" s="2">
         <v>81</v>
@@ -25168,963 +25148,17 @@
         <v>81</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>287</v>
+        <v>497</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="193" hidden="true">
-      <c r="A193" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="C193" s="2"/>
-      <c r="D193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G193" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J193" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K193" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N193" s="2"/>
-      <c r="O193" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="P193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q193" s="2"/>
-      <c r="R193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X193" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y193" s="2"/>
-      <c r="Z193" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AG193" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH193" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ193" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AN193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO193" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="194" hidden="true">
-      <c r="A194" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C194" s="2"/>
-      <c r="D194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E194" s="2"/>
-      <c r="F194" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G194" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J194" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K194" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L194" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="P194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q194" s="2"/>
-      <c r="R194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF194" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AG194" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH194" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ194" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM194" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AN194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO194" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="195" hidden="true">
-      <c r="A195" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C195" s="2"/>
-      <c r="D195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E195" s="2"/>
-      <c r="F195" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G195" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J195" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K195" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="L195" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="P195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q195" s="2"/>
-      <c r="R195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF195" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG195" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH195" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ195" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM195" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AN195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO195" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="196" hidden="true">
-      <c r="A196" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C196" s="2"/>
-      <c r="D196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E196" s="2"/>
-      <c r="F196" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G196" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J196" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K196" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L196" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="P196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q196" s="2"/>
-      <c r="R196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF196" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AG196" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH196" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ196" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM196" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AN196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO196" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="197" hidden="true">
-      <c r="A197" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C197" s="2"/>
-      <c r="D197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E197" s="2"/>
-      <c r="F197" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G197" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J197" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K197" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="L197" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O197" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="P197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q197" s="2"/>
-      <c r="R197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF197" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AG197" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH197" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ197" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL197" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AM197" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AN197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO197" t="s" s="2">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="198" hidden="true">
-      <c r="A198" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C198" s="2"/>
-      <c r="D198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E198" s="2"/>
-      <c r="F198" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G198" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K198" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L198" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N198" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O198" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="P198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q198" s="2"/>
-      <c r="R198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X198" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y198" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="Z198" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AA198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF198" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG198" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH198" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI198" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AJ198" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM198" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AN198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO198" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="199" hidden="true">
-      <c r="A199" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="C199" s="2"/>
-      <c r="D199" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="E199" s="2"/>
-      <c r="F199" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G199" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K199" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L199" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="M199" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O199" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="P199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q199" s="2"/>
-      <c r="R199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X199" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y199" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="Z199" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AA199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF199" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AG199" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH199" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ199" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL199" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AM199" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AN199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO199" t="s" s="2">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="200" hidden="true">
-      <c r="A200" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C200" s="2"/>
-      <c r="D200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E200" s="2"/>
-      <c r="F200" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G200" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L200" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="M200" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="P200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q200" s="2"/>
-      <c r="R200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF200" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AG200" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH200" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ200" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM200" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AN200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO200" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO200">
+  <autoFilter ref="A1:AO192">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -26134,7 +25168,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI199">
+  <conditionalFormatting sqref="A2:AI191">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
@@ -2164,7 +2164,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="1078210003"/&gt;
   &lt;display value="Z-score calculation technique (qualifier value)"/&gt;
 &lt;/valueCoding&gt;</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-prozent.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$157</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7205" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="662">
   <si>
     <t>Property</t>
   </si>
@@ -988,6 +988,9 @@
     <t>Ein Verweis auf einen von SNOMED CT definierten Code</t>
   </si>
   <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-sct-observable</t>
+  </si>
+  <si>
     <t>Observation.code.coding:sct.id</t>
   </si>
   <si>
@@ -1003,9 +1006,6 @@
     <t>Observation.code.coding:sct.code</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-sct-observable</t>
-  </si>
-  <si>
     <t>Observation.code.coding:sct.display</t>
   </si>
   <si>
@@ -1024,6 +1024,9 @@
     <t>Ein Verweis auf einen vom LOINC definierten Code</t>
   </si>
   <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-observable</t>
+  </si>
+  <si>
     <t>Observation.code.coding:loinc.id</t>
   </si>
   <si>
@@ -1037,9 +1040,6 @@
   </si>
   <si>
     <t>Observation.code.coding:loinc.code</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/ValueSet/mii-vs-lufu-lnc-observable</t>
   </si>
   <si>
     <t>Observation.code.coding:loinc.display</t>
@@ -1870,70 +1870,7 @@
     <t>Observation.component:predicted.code.coding:sct</t>
   </si>
   <si>
-    <t>Observation.component:predicted.code.coding:sct.id</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.system</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.version</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.code</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.display</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:sct.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.userSelected</t>
-  </si>
-  <si>
     <t>Observation.component:predicted.code.coding:loinc</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.system</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.version</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.code</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.display</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code.coding:loinc.userSelected</t>
   </si>
   <si>
     <t>Observation.component:predicted.code.text</t>
@@ -2042,49 +1979,7 @@
     <t>Observation.component:percentPredicted.code.coding:sct</t>
   </si>
   <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.id</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.system</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.version</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.code</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.display</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:sct.userSelected</t>
-  </si>
-  <si>
     <t>Observation.component:percentPredicted.code.coding:loinc</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.id</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.system</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.version</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.code</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.display</t>
-  </si>
-  <si>
-    <t>Observation.component:percentPredicted.code.coding:loinc.userSelected</t>
   </si>
   <si>
     <t>Observation.component:percentPredicted.code.text</t>
@@ -2164,31 +2059,10 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
   &lt;code value="1078210003"/&gt;
   &lt;display value="Z-score calculation technique (qualifier value)"/&gt;
 &lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.id</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.system</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.version</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.code</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.display</t>
-  </si>
-  <si>
-    <t>Observation.component:z-score.code.coding:sct.userSelected</t>
   </si>
   <si>
     <t>Observation.component:z-score.code.text</t>
@@ -2520,11 +2394,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO192"/>
+  <dimension ref="A1:AO157"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.09765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.64453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -7092,13 +6966,11 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -7148,7 +7020,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>273</v>
@@ -7263,7 +7135,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>274</v>
@@ -7380,7 +7252,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>275</v>
@@ -7499,7 +7371,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>282</v>
@@ -7616,7 +7488,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>288</v>
@@ -7677,11 +7549,13 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -8032,13 +7906,11 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>81</v>
+        <v>324</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -8088,7 +7960,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>273</v>
@@ -8203,7 +8075,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>274</v>
@@ -8320,7 +8192,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>275</v>
@@ -8439,7 +8311,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>282</v>
@@ -8556,7 +8428,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>288</v>
@@ -8617,11 +8489,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -14975,13 +14849,11 @@
         <v>81</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>81</v>
@@ -15029,14 +14901,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>594</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="C107" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="D107" t="s" s="2">
         <v>81</v>
       </c>
@@ -15048,25 +14922,29 @@
         <v>91</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>106</v>
+        <v>322</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
       </c>
@@ -15090,13 +14968,11 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>81</v>
+        <v>324</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
@@ -15114,19 +14990,19 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>108</v>
+        <v>248</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>81</v>
@@ -15135,7 +15011,7 @@
         <v>81</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>81</v>
@@ -15146,21 +15022,21 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>81</v>
@@ -15169,21 +15045,23 @@
         <v>81</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>112</v>
+        <v>251</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>113</v>
+        <v>252</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O108" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
       </c>
@@ -15219,31 +15097,31 @@
         <v>81</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>118</v>
+        <v>255</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>81</v>
@@ -15252,7 +15130,7 @@
         <v>81</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>81</v>
+        <v>256</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>81</v>
@@ -15263,10 +15141,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>599</v>
+        <v>563</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15289,19 +15167,19 @@
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>132</v>
+        <v>564</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>276</v>
+        <v>565</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>277</v>
+        <v>566</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>278</v>
+        <v>567</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>279</v>
+        <v>386</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -15338,19 +15216,17 @@
         <v>81</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="AC109" s="2"/>
       <c r="AD109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>280</v>
+        <v>563</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15368,26 +15244,28 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>281</v>
+        <v>389</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C110" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="B110" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>81</v>
       </c>
@@ -15408,18 +15286,20 @@
         <v>92</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>105</v>
+        <v>382</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>283</v>
+        <v>565</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>284</v>
+        <v>566</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O110" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
       </c>
@@ -15467,7 +15347,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>286</v>
+        <v>563</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15485,24 +15365,24 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>287</v>
+        <v>389</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15522,21 +15402,19 @@
         <v>81</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>289</v>
+        <v>106</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>290</v>
+        <v>107</v>
       </c>
       <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>291</v>
-      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>81</v>
       </c>
@@ -15560,11 +15438,13 @@
         <v>81</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
@@ -15582,7 +15462,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>292</v>
+        <v>108</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15594,7 +15474,7 @@
         <v>81</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>81</v>
@@ -15603,7 +15483,7 @@
         <v>81</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>81</v>
@@ -15614,21 +15494,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>81</v>
@@ -15637,21 +15517,21 @@
         <v>81</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>295</v>
+        <v>112</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>81</v>
       </c>
@@ -15687,31 +15567,31 @@
         <v>81</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>298</v>
+        <v>118</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>81</v>
@@ -15720,7 +15600,7 @@
         <v>81</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>299</v>
+        <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>81</v>
@@ -15729,12 +15609,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15748,7 +15628,7 @@
         <v>91</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>81</v>
@@ -15757,19 +15637,19 @@
         <v>92</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>301</v>
+        <v>394</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>302</v>
+        <v>395</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>303</v>
+        <v>396</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>304</v>
+        <v>397</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>305</v>
+        <v>398</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15818,7 +15698,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>306</v>
+        <v>399</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15839,7 +15719,7 @@
         <v>81</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>307</v>
+        <v>400</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
@@ -15848,16 +15728,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="B114" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C114" t="s" s="2">
-        <v>321</v>
-      </c>
+      <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>81</v>
       </c>
@@ -15869,33 +15747,33 @@
         <v>91</v>
       </c>
       <c r="H114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I114" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J114" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>322</v>
+        <v>402</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>246</v>
+        <v>404</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q114" s="2"/>
+      <c r="Q114" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="R114" t="s" s="2">
         <v>81</v>
       </c>
@@ -15915,13 +15793,13 @@
         <v>81</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>81</v>
@@ -15939,13 +15817,13 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>248</v>
+        <v>408</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>81</v>
@@ -15960,7 +15838,7 @@
         <v>81</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>249</v>
+        <v>409</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
@@ -15969,12 +15847,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>609</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15988,25 +15866,27 @@
         <v>91</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>106</v>
+        <v>411</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>107</v>
+        <v>412</v>
       </c>
       <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>81</v>
       </c>
@@ -16015,7 +15895,7 @@
         <v>81</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>81</v>
@@ -16054,7 +15934,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>108</v>
+        <v>415</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16066,7 +15946,7 @@
         <v>81</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>81</v>
@@ -16075,7 +15955,7 @@
         <v>81</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>81</v>
@@ -16084,46 +15964,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>112</v>
+        <v>418</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
       </c>
@@ -16132,7 +16012,7 @@
         <v>81</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>81</v>
@@ -16159,31 +16039,31 @@
         <v>81</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>118</v>
+        <v>422</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>81</v>
@@ -16192,7 +16072,7 @@
         <v>81</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>81</v>
@@ -16201,12 +16081,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>599</v>
+        <v>614</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16220,7 +16100,7 @@
         <v>91</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>81</v>
@@ -16229,19 +16109,19 @@
         <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>276</v>
+        <v>425</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>278</v>
+        <v>427</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>279</v>
+        <v>428</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
@@ -16251,7 +16131,7 @@
         <v>81</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>81</v>
@@ -16290,7 +16170,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>280</v>
+        <v>429</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16311,7 +16191,7 @@
         <v>81</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>281</v>
+        <v>416</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>81</v>
@@ -16322,10 +16202,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>601</v>
+        <v>569</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16345,21 +16225,23 @@
         <v>81</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>283</v>
+        <v>570</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>284</v>
+        <v>571</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O118" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16383,13 +16265,13 @@
         <v>81</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>81</v>
@@ -16407,7 +16289,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>286</v>
+        <v>569</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16416,7 +16298,7 @@
         <v>91</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>103</v>
@@ -16428,7 +16310,7 @@
         <v>81</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>287</v>
+        <v>438</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>81</v>
@@ -16439,21 +16321,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>603</v>
+        <v>573</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>81</v>
@@ -16462,20 +16344,22 @@
         <v>81</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>289</v>
+        <v>574</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O119" t="s" s="2">
-        <v>291</v>
+        <v>444</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>81</v>
@@ -16500,11 +16384,13 @@
         <v>81</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y119" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="Z119" t="s" s="2">
-        <v>329</v>
+        <v>446</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>81</v>
@@ -16522,13 +16408,13 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>292</v>
+        <v>573</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>81</v>
@@ -16540,24 +16426,24 @@
         <v>81</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>293</v>
+        <v>448</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16568,7 +16454,7 @@
         <v>79</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>81</v>
@@ -16577,20 +16463,22 @@
         <v>81</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>295</v>
+        <v>577</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="O120" t="s" s="2">
-        <v>297</v>
+        <v>495</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16639,13 +16527,13 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>298</v>
+        <v>576</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>81</v>
@@ -16660,7 +16548,7 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>299</v>
+        <v>497</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
@@ -16669,14 +16557,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C121" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>619</v>
+      </c>
       <c r="D121" t="s" s="2">
         <v>81</v>
       </c>
@@ -16688,7 +16578,7 @@
         <v>91</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>81</v>
@@ -16697,19 +16587,19 @@
         <v>92</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>301</v>
+        <v>491</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>302</v>
+        <v>620</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>303</v>
+        <v>621</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>304</v>
+        <v>552</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>305</v>
+        <v>553</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
@@ -16758,13 +16648,13 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>306</v>
+        <v>549</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>81</v>
@@ -16779,7 +16669,7 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>307</v>
+        <v>554</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -16790,10 +16680,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>617</v>
+        <v>555</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16813,23 +16703,19 @@
         <v>81</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K122" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>251</v>
+        <v>106</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>81</v>
       </c>
@@ -16877,7 +16763,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16889,7 +16775,7 @@
         <v>81</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>81</v>
@@ -16898,7 +16784,7 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>256</v>
+        <v>81</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
@@ -16909,21 +16795,21 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>81</v>
@@ -16932,23 +16818,21 @@
         <v>81</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>564</v>
+        <v>111</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>565</v>
+        <v>112</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>566</v>
+        <v>113</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>81</v>
       </c>
@@ -16984,89 +16868,89 @@
         <v>81</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AC123" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>563</v>
+        <v>118</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>621</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J124" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>382</v>
+        <v>111</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>565</v>
+        <v>502</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>566</v>
+        <v>503</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>567</v>
+        <v>114</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>386</v>
+        <v>194</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17115,42 +16999,42 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>563</v>
+        <v>504</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>623</v>
+        <v>558</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17158,7 +17042,7 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G125" t="s" s="2">
         <v>91</v>
@@ -17170,19 +17054,23 @@
         <v>81</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>106</v>
+        <v>559</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
       </c>
@@ -17206,13 +17094,13 @@
         <v>81</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>81</v>
@@ -17230,10 +17118,10 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>108</v>
+        <v>558</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>91</v>
@@ -17242,19 +17130,19 @@
         <v>81</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>81</v>
+        <v>562</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>81</v>
@@ -17262,21 +17150,21 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>625</v>
+        <v>588</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>81</v>
@@ -17288,17 +17176,15 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>81</v>
@@ -17335,31 +17221,31 @@
         <v>81</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>81</v>
@@ -17377,48 +17263,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>627</v>
+        <v>590</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>394</v>
+        <v>111</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>395</v>
+        <v>112</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>396</v>
+        <v>113</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>81</v>
       </c>
@@ -17454,31 +17338,31 @@
         <v>81</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>399</v>
+        <v>118</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>81</v>
@@ -17487,7 +17371,7 @@
         <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>400</v>
+        <v>81</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>81</v>
@@ -17501,7 +17385,7 @@
         <v>628</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>629</v>
+        <v>592</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17512,36 +17396,36 @@
         <v>79</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J128" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>402</v>
+        <v>243</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N128" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O128" t="s" s="2">
-        <v>404</v>
+        <v>246</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q128" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
         <v>81</v>
       </c>
@@ -17561,37 +17445,35 @@
         <v>81</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC128" s="2"/>
       <c r="AD128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>408</v>
+        <v>248</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>81</v>
@@ -17606,7 +17488,7 @@
         <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>409</v>
+        <v>249</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>81</v>
@@ -17617,12 +17499,14 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="C129" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="D129" t="s" s="2">
         <v>81</v>
       </c>
@@ -17643,17 +17527,19 @@
         <v>92</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>411</v>
+        <v>310</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N129" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O129" t="s" s="2">
-        <v>413</v>
+        <v>246</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>81</v>
@@ -17663,7 +17549,7 @@
         <v>81</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>81</v>
@@ -17678,13 +17564,11 @@
         <v>81</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>81</v>
@@ -17702,13 +17586,13 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>415</v>
+        <v>248</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>81</v>
@@ -17723,7 +17607,7 @@
         <v>81</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>416</v>
+        <v>249</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>
@@ -17734,12 +17618,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="C130" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="D130" t="s" s="2">
         <v>81</v>
       </c>
@@ -17760,17 +17646,19 @@
         <v>92</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>418</v>
+        <v>322</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N130" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O130" t="s" s="2">
-        <v>420</v>
+        <v>246</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>81</v>
@@ -17780,7 +17668,7 @@
         <v>81</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>81</v>
@@ -17795,13 +17683,11 @@
         <v>81</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
-        <v>81</v>
+        <v>324</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>81</v>
@@ -17819,16 +17705,16 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>422</v>
+        <v>248</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>103</v>
@@ -17840,7 +17726,7 @@
         <v>81</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>416</v>
+        <v>249</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>81</v>
@@ -17849,12 +17735,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>635</v>
+        <v>596</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17868,7 +17754,7 @@
         <v>91</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>81</v>
@@ -17877,19 +17763,19 @@
         <v>92</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>425</v>
+        <v>251</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>426</v>
+        <v>252</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>427</v>
+        <v>253</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>428</v>
+        <v>254</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
@@ -17899,7 +17785,7 @@
         <v>81</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>81</v>
@@ -17938,7 +17824,7 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>429</v>
+        <v>255</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17959,7 +17845,7 @@
         <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>416</v>
+        <v>256</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>81</v>
@@ -17970,10 +17856,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17993,22 +17879,22 @@
         <v>81</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>232</v>
+        <v>564</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>434</v>
+        <v>386</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
@@ -18033,31 +17919,29 @@
         <v>81</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="AC132" s="2"/>
       <c r="AD132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18066,7 +17950,7 @@
         <v>91</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>103</v>
@@ -18075,35 +17959,37 @@
         <v>81</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C133" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="D133" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>81</v>
@@ -18112,22 +17998,22 @@
         <v>81</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>232</v>
+        <v>382</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>443</v>
+        <v>567</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>444</v>
+        <v>386</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>81</v>
@@ -18152,13 +18038,13 @@
         <v>81</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>81</v>
@@ -18176,13 +18062,13 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>81</v>
@@ -18194,24 +18080,24 @@
         <v>81</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>447</v>
+        <v>568</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>448</v>
+        <v>389</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>449</v>
+        <v>390</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18222,7 +18108,7 @@
         <v>79</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>81</v>
@@ -18234,20 +18120,16 @@
         <v>81</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>577</v>
+        <v>106</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>81</v>
       </c>
@@ -18295,19 +18177,19 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>576</v>
+        <v>108</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>81</v>
@@ -18316,7 +18198,7 @@
         <v>81</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>81</v>
@@ -18325,50 +18207,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>640</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>641</v>
+        <v>112</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>642</v>
+        <v>113</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>81</v>
       </c>
@@ -18404,19 +18282,19 @@
         <v>81</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>549</v>
+        <v>118</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18428,7 +18306,7 @@
         <v>81</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>81</v>
@@ -18437,7 +18315,7 @@
         <v>81</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>554</v>
+        <v>81</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -18446,12 +18324,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>555</v>
+        <v>606</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18465,25 +18343,29 @@
         <v>91</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>105</v>
+        <v>394</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>106</v>
+        <v>395</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P136" t="s" s="2">
         <v>81</v>
       </c>
@@ -18531,7 +18413,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>108</v>
+        <v>399</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18543,7 +18425,7 @@
         <v>81</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>81</v>
@@ -18552,7 +18434,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>81</v>
+        <v>400</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -18563,48 +18445,50 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>556</v>
+        <v>608</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I137" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>112</v>
+        <v>402</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O137" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q137" s="2"/>
+      <c r="Q137" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="R137" t="s" s="2">
         <v>81</v>
       </c>
@@ -18624,13 +18508,13 @@
         <v>81</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>81</v>
@@ -18648,19 +18532,19 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>118</v>
+        <v>408</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>81</v>
@@ -18669,7 +18553,7 @@
         <v>81</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>
@@ -18678,47 +18562,45 @@
         <v>81</v>
       </c>
     </row>
-    <row r="138" hidden="true">
+    <row r="138">
       <c r="A138" t="s" s="2">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>557</v>
+        <v>610</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>501</v>
+        <v>81</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J138" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>502</v>
+        <v>411</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>194</v>
+        <v>413</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>81</v>
@@ -18728,7 +18610,7 @@
         <v>81</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>81</v>
@@ -18767,19 +18649,19 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>504</v>
+        <v>415</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>81</v>
@@ -18788,7 +18670,7 @@
         <v>81</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>81</v>
@@ -18797,12 +18679,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>558</v>
+        <v>612</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18810,13 +18692,13 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>81</v>
@@ -18825,19 +18707,17 @@
         <v>92</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>232</v>
+        <v>132</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>559</v>
+        <v>418</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>261</v>
+        <v>420</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>81</v>
@@ -18847,7 +18727,7 @@
         <v>81</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>81</v>
@@ -18862,13 +18742,13 @@
         <v>81</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>81</v>
@@ -18886,16 +18766,16 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>558</v>
+        <v>422</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>103</v>
@@ -18904,24 +18784,24 @@
         <v>81</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>562</v>
+        <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>266</v>
+        <v>416</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="140" hidden="true">
+    <row r="140">
       <c r="A140" t="s" s="2">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18935,25 +18815,29 @@
         <v>91</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>106</v>
+        <v>425</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>81</v>
       </c>
@@ -18962,7 +18846,7 @@
         <v>81</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>81</v>
@@ -19001,7 +18885,7 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>108</v>
+        <v>429</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19013,7 +18897,7 @@
         <v>81</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>81</v>
@@ -19022,7 +18906,7 @@
         <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>81</v>
@@ -19033,21 +18917,21 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>81</v>
@@ -19059,18 +18943,20 @@
         <v>81</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>112</v>
+        <v>570</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>113</v>
+        <v>571</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O141" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>81</v>
       </c>
@@ -19094,43 +18980,43 @@
         <v>81</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>118</v>
+        <v>569</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>81</v>
@@ -19139,7 +19025,7 @@
         <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>81</v>
@@ -19150,14 +19036,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>592</v>
+        <v>573</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -19173,22 +19059,22 @@
         <v>81</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>144</v>
+        <v>232</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>243</v>
+        <v>574</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>244</v>
+        <v>575</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>245</v>
+        <v>443</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>246</v>
+        <v>444</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>81</v>
@@ -19213,29 +19099,31 @@
         <v>81</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>81</v>
+        <v>446</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC142" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>248</v>
+        <v>573</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19253,28 +19141,26 @@
         <v>81</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>249</v>
+        <v>448</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
         <v>81</v>
       </c>
@@ -19283,31 +19169,31 @@
         <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>310</v>
+        <v>577</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>311</v>
+        <v>578</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>245</v>
+        <v>494</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>246</v>
+        <v>495</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -19356,7 +19242,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>248</v>
+        <v>576</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19377,7 +19263,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>249</v>
+        <v>497</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -19386,14 +19272,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="144" hidden="true">
+    <row r="144">
       <c r="A144" t="s" s="2">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="C144" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="D144" t="s" s="2">
         <v>81</v>
       </c>
@@ -19405,25 +19293,29 @@
         <v>91</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>105</v>
+        <v>491</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>106</v>
+        <v>646</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N144" s="2"/>
-      <c r="O144" s="2"/>
+        <v>647</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>81</v>
       </c>
@@ -19471,19 +19363,19 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>108</v>
+        <v>549</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>81</v>
@@ -19492,7 +19384,7 @@
         <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>81</v>
+        <v>554</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>81</v>
@@ -19503,21 +19395,21 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>597</v>
+        <v>555</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>81</v>
@@ -19529,17 +19421,15 @@
         <v>81</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>81</v>
@@ -19576,31 +19466,31 @@
         <v>81</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>81</v>
@@ -19620,21 +19510,21 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>599</v>
+        <v>556</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>81</v>
@@ -19643,23 +19533,21 @@
         <v>81</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>276</v>
+        <v>112</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>277</v>
+        <v>113</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>81</v>
       </c>
@@ -19707,19 +19595,19 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>280</v>
+        <v>118</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>81</v>
@@ -19728,7 +19616,7 @@
         <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>281</v>
+        <v>81</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>81</v>
@@ -19739,44 +19627,46 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>601</v>
+        <v>557</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I147" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J147" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>283</v>
+        <v>502</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>284</v>
+        <v>503</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O147" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="P147" t="s" s="2">
         <v>81</v>
       </c>
@@ -19824,19 +19714,19 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>286</v>
+        <v>504</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>81</v>
@@ -19845,7 +19735,7 @@
         <v>81</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>287</v>
+        <v>81</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>81</v>
@@ -19856,10 +19746,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>603</v>
+        <v>558</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19867,7 +19757,7 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>91</v>
@@ -19882,17 +19772,19 @@
         <v>92</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>289</v>
+        <v>559</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N148" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="O148" t="s" s="2">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>81</v>
@@ -19917,11 +19809,13 @@
         <v>81</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y148" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="Z148" t="s" s="2">
-        <v>317</v>
+        <v>263</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>81</v>
@@ -19939,10 +19833,10 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>292</v>
+        <v>558</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>91</v>
@@ -19957,13 +19851,13 @@
         <v>81</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>81</v>
+        <v>562</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>81</v>
@@ -19971,10 +19865,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19994,21 +19888,19 @@
         <v>81</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K149" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>295</v>
+        <v>106</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>296</v>
+        <v>107</v>
       </c>
       <c r="N149" s="2"/>
-      <c r="O149" t="s" s="2">
-        <v>297</v>
-      </c>
+      <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>81</v>
       </c>
@@ -20056,7 +19948,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>298</v>
+        <v>108</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20068,7 +19960,7 @@
         <v>81</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>81</v>
@@ -20077,7 +19969,7 @@
         <v>81</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>299</v>
+        <v>81</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>81</v>
@@ -20088,21 +19980,21 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>81</v>
@@ -20111,23 +20003,21 @@
         <v>81</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>301</v>
+        <v>111</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>302</v>
+        <v>112</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>303</v>
+        <v>113</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>81</v>
       </c>
@@ -20163,31 +20053,31 @@
         <v>81</v>
       </c>
       <c r="AB150" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC150" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>306</v>
+        <v>118</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>81</v>
@@ -20196,7 +20086,7 @@
         <v>81</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>81</v>
@@ -20205,16 +20095,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="C151" t="s" s="2">
-        <v>321</v>
-      </c>
+      <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>81</v>
       </c>
@@ -20223,10 +20111,10 @@
         <v>79</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>81</v>
@@ -20238,10 +20126,10 @@
         <v>144</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>322</v>
+        <v>243</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>323</v>
+        <v>244</v>
       </c>
       <c r="N151" t="s" s="2">
         <v>245</v>
@@ -20284,16 +20172,14 @@
         <v>81</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC151" s="2"/>
       <c r="AD151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF151" t="s" s="2">
         <v>248</v>
@@ -20326,14 +20212,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="C152" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="D152" t="s" s="2">
         <v>81</v>
       </c>
@@ -20345,25 +20233,29 @@
         <v>91</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>106</v>
+        <v>310</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N152" s="2"/>
-      <c r="O152" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P152" t="s" s="2">
         <v>81</v>
       </c>
@@ -20372,7 +20264,7 @@
         <v>81</v>
       </c>
       <c r="S152" t="s" s="2">
-        <v>81</v>
+        <v>656</v>
       </c>
       <c r="T152" t="s" s="2">
         <v>81</v>
@@ -20387,13 +20279,11 @@
         <v>81</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>81</v>
@@ -20411,19 +20301,19 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>108</v>
+        <v>248</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>81</v>
@@ -20432,7 +20322,7 @@
         <v>81</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>81</v>
@@ -20443,21 +20333,21 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>81</v>
@@ -20466,21 +20356,23 @@
         <v>81</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>112</v>
+        <v>251</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>113</v>
+        <v>252</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O153" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>81</v>
       </c>
@@ -20516,31 +20408,31 @@
         <v>81</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>118</v>
+        <v>255</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>81</v>
@@ -20549,7 +20441,7 @@
         <v>81</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>81</v>
+        <v>256</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>81</v>
@@ -20560,10 +20452,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>599</v>
+        <v>563</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20586,19 +20478,19 @@
         <v>92</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>132</v>
+        <v>564</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>276</v>
+        <v>565</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>277</v>
+        <v>566</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>278</v>
+        <v>567</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>279</v>
+        <v>386</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>81</v>
@@ -20647,7 +20539,7 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>280</v>
+        <v>563</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20665,24 +20557,24 @@
         <v>81</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>81</v>
+        <v>568</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>281</v>
+        <v>389</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>601</v>
+        <v>569</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20702,21 +20594,23 @@
         <v>81</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>283</v>
+        <v>570</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>284</v>
+        <v>571</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O155" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>81</v>
       </c>
@@ -20740,13 +20634,13 @@
         <v>81</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>81</v>
@@ -20764,7 +20658,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>286</v>
+        <v>569</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -20773,7 +20667,7 @@
         <v>91</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>103</v>
@@ -20785,7 +20679,7 @@
         <v>81</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>287</v>
+        <v>438</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>81</v>
@@ -20796,21 +20690,21 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>603</v>
+        <v>573</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>81</v>
@@ -20819,20 +20713,22 @@
         <v>81</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>289</v>
+        <v>574</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N156" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O156" t="s" s="2">
-        <v>291</v>
+        <v>444</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>81</v>
@@ -20857,11 +20753,13 @@
         <v>81</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y156" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="Z156" t="s" s="2">
-        <v>329</v>
+        <v>446</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>81</v>
@@ -20879,13 +20777,13 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>292</v>
+        <v>573</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>81</v>
@@ -20897,24 +20795,24 @@
         <v>81</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>293</v>
+        <v>448</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20925,7 +20823,7 @@
         <v>79</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>81</v>
@@ -20934,20 +20832,22 @@
         <v>81</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>295</v>
+        <v>577</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N157" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="O157" t="s" s="2">
-        <v>297</v>
+        <v>495</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -20996,13 +20896,13 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>298</v>
+        <v>576</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>81</v>
@@ -21017,4148 +20917,17 @@
         <v>81</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>299</v>
+        <v>497</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="158" hidden="true">
-      <c r="A158" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C158" s="2"/>
-      <c r="D158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E158" s="2"/>
-      <c r="F158" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G158" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J158" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K158" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="P158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q158" s="2"/>
-      <c r="R158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH158" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ158" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM158" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AN158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO158" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="159" hidden="true">
-      <c r="A159" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C159" s="2"/>
-      <c r="D159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E159" s="2"/>
-      <c r="F159" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K159" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L159" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="P159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q159" s="2"/>
-      <c r="R159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF159" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AG159" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ159" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO159" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="160" hidden="true">
-      <c r="A160" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C160" s="2"/>
-      <c r="D160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E160" s="2"/>
-      <c r="F160" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G160" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J160" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K160" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="L160" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="P160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q160" s="2"/>
-      <c r="R160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AC160" s="2"/>
-      <c r="AD160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH160" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ160" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL160" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO160" t="s" s="2">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="161" hidden="true">
-      <c r="A161" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C161" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="D161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E161" s="2"/>
-      <c r="F161" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G161" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J161" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K161" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="L161" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="P161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q161" s="2"/>
-      <c r="R161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AG161" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH161" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ161" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL161" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO161" t="s" s="2">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="162" hidden="true">
-      <c r="A162" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C162" s="2"/>
-      <c r="D162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E162" s="2"/>
-      <c r="F162" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G162" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K162" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L162" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N162" s="2"/>
-      <c r="O162" s="2"/>
-      <c r="P162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q162" s="2"/>
-      <c r="R162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF162" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG162" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH162" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN162" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO162" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="163" hidden="true">
-      <c r="A163" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="C163" s="2"/>
-      <c r="D163" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E163" s="2"/>
-      <c r="F163" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K163" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L163" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O163" s="2"/>
-      <c r="P163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q163" s="2"/>
-      <c r="R163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC163" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE163" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF163" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG163" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ163" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO163" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="C164" s="2"/>
-      <c r="D164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E164" s="2"/>
-      <c r="F164" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G164" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H164" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J164" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K164" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="L164" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="P164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q164" s="2"/>
-      <c r="R164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF164" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AG164" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH164" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ164" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM164" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AN164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO164" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="165" hidden="true">
-      <c r="A165" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="C165" s="2"/>
-      <c r="D165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E165" s="2"/>
-      <c r="F165" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G165" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I165" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J165" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K165" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L165" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N165" s="2"/>
-      <c r="O165" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="P165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q165" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="R165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X165" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y165" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="Z165" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AA165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF165" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AG165" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH165" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ165" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM165" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AN165" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO165" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="C166" s="2"/>
-      <c r="D166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E166" s="2"/>
-      <c r="F166" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G166" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H166" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J166" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K166" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L166" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N166" s="2"/>
-      <c r="O166" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="P166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q166" s="2"/>
-      <c r="R166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S166" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="T166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF166" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AG166" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH166" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ166" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM166" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO166" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="C167" s="2"/>
-      <c r="D167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E167" s="2"/>
-      <c r="F167" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G167" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H167" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J167" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K167" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L167" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N167" s="2"/>
-      <c r="O167" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="P167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q167" s="2"/>
-      <c r="R167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S167" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="T167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF167" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AG167" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH167" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI167" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AJ167" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM167" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO167" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C168" s="2"/>
-      <c r="D168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E168" s="2"/>
-      <c r="F168" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G168" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H168" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J168" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K168" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L168" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="P168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q168" s="2"/>
-      <c r="R168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S168" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="T168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF168" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AG168" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH168" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ168" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM168" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO168" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="169" hidden="true">
-      <c r="A169" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="C169" s="2"/>
-      <c r="D169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E169" s="2"/>
-      <c r="F169" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G169" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K169" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L169" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="P169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q169" s="2"/>
-      <c r="R169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X169" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y169" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="Z169" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AA169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF169" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AG169" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH169" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI169" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AJ169" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM169" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AN169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO169" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="170" hidden="true">
-      <c r="A170" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C170" s="2"/>
-      <c r="D170" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="E170" s="2"/>
-      <c r="F170" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G170" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K170" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L170" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="P170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q170" s="2"/>
-      <c r="R170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X170" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y170" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="Z170" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AA170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF170" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AG170" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH170" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ170" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL170" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AM170" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AN170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO170" t="s" s="2">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="171" hidden="true">
-      <c r="A171" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="C171" s="2"/>
-      <c r="D171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E171" s="2"/>
-      <c r="F171" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G171" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L171" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="P171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q171" s="2"/>
-      <c r="R171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF171" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AG171" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH171" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ171" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM171" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AN171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO171" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="C172" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="D172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E172" s="2"/>
-      <c r="F172" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G172" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H172" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J172" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K172" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="L172" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="P172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q172" s="2"/>
-      <c r="R172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF172" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AG172" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH172" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ172" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM172" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AN172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO172" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="173" hidden="true">
-      <c r="A173" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="C173" s="2"/>
-      <c r="D173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E173" s="2"/>
-      <c r="F173" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G173" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K173" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L173" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N173" s="2"/>
-      <c r="O173" s="2"/>
-      <c r="P173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q173" s="2"/>
-      <c r="R173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF173" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG173" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH173" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO173" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="174" hidden="true">
-      <c r="A174" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C174" s="2"/>
-      <c r="D174" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E174" s="2"/>
-      <c r="F174" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G174" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K174" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L174" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O174" s="2"/>
-      <c r="P174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q174" s="2"/>
-      <c r="R174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF174" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG174" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH174" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ174" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO174" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="175" hidden="true">
-      <c r="A175" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="C175" s="2"/>
-      <c r="D175" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="E175" s="2"/>
-      <c r="F175" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G175" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I175" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J175" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K175" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L175" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="P175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q175" s="2"/>
-      <c r="R175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF175" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AG175" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH175" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ175" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO175" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="176" hidden="true">
-      <c r="A176" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="C176" s="2"/>
-      <c r="D176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E176" s="2"/>
-      <c r="F176" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G176" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J176" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K176" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L176" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="P176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q176" s="2"/>
-      <c r="R176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X176" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y176" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="Z176" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AA176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF176" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AG176" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH176" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ176" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL176" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AM176" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AN176" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AO176" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="177" hidden="true">
-      <c r="A177" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C177" s="2"/>
-      <c r="D177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E177" s="2"/>
-      <c r="F177" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G177" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K177" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L177" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N177" s="2"/>
-      <c r="O177" s="2"/>
-      <c r="P177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q177" s="2"/>
-      <c r="R177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF177" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG177" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH177" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="178" hidden="true">
-      <c r="A178" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="C178" s="2"/>
-      <c r="D178" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E178" s="2"/>
-      <c r="F178" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G178" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K178" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L178" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O178" s="2"/>
-      <c r="P178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q178" s="2"/>
-      <c r="R178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB178" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE178" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF178" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG178" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH178" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ178" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO178" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="179" hidden="true">
-      <c r="A179" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C179" s="2"/>
-      <c r="D179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E179" s="2"/>
-      <c r="F179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G179" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J179" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K179" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="L179" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="P179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q179" s="2"/>
-      <c r="R179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC179" s="2"/>
-      <c r="AD179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AG179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH179" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ179" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM179" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AN179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO179" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C180" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="D180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E180" s="2"/>
-      <c r="F180" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G180" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H180" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J180" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K180" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="L180" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="P180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q180" s="2"/>
-      <c r="R180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S180" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="T180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF180" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AG180" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH180" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ180" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM180" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AN180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO180" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="181" hidden="true">
-      <c r="A181" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="C181" s="2"/>
-      <c r="D181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E181" s="2"/>
-      <c r="F181" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G181" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K181" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L181" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N181" s="2"/>
-      <c r="O181" s="2"/>
-      <c r="P181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q181" s="2"/>
-      <c r="R181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF181" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG181" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH181" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO181" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="182" hidden="true">
-      <c r="A182" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C182" s="2"/>
-      <c r="D182" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E182" s="2"/>
-      <c r="F182" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G182" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K182" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L182" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O182" s="2"/>
-      <c r="P182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q182" s="2"/>
-      <c r="R182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB182" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC182" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE182" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF182" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG182" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH182" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ182" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO182" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="183" hidden="true">
-      <c r="A183" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="C183" s="2"/>
-      <c r="D183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E183" s="2"/>
-      <c r="F183" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G183" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J183" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K183" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L183" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="P183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q183" s="2"/>
-      <c r="R183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF183" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AG183" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH183" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ183" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM183" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO183" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="184" hidden="true">
-      <c r="A184" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C184" s="2"/>
-      <c r="D184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E184" s="2"/>
-      <c r="F184" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G184" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J184" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K184" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L184" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O184" s="2"/>
-      <c r="P184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q184" s="2"/>
-      <c r="R184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF184" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AG184" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH184" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ184" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM184" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AN184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO184" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="185" hidden="true">
-      <c r="A185" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="C185" s="2"/>
-      <c r="D185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E185" s="2"/>
-      <c r="F185" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G185" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J185" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K185" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L185" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N185" s="2"/>
-      <c r="O185" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="P185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q185" s="2"/>
-      <c r="R185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X185" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y185" s="2"/>
-      <c r="Z185" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AG185" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH185" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ185" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM185" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AN185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO185" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="186" hidden="true">
-      <c r="A186" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C186" s="2"/>
-      <c r="D186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E186" s="2"/>
-      <c r="F186" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G186" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J186" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K186" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L186" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="P186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q186" s="2"/>
-      <c r="R186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF186" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AG186" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH186" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ186" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM186" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AN186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO186" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="187" hidden="true">
-      <c r="A187" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C187" s="2"/>
-      <c r="D187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E187" s="2"/>
-      <c r="F187" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G187" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J187" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K187" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="P187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q187" s="2"/>
-      <c r="R187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ187" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM187" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO187" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="188" hidden="true">
-      <c r="A188" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C188" s="2"/>
-      <c r="D188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E188" s="2"/>
-      <c r="F188" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G188" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J188" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K188" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L188" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="P188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q188" s="2"/>
-      <c r="R188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF188" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AG188" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH188" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ188" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM188" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO188" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="189" hidden="true">
-      <c r="A189" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C189" s="2"/>
-      <c r="D189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E189" s="2"/>
-      <c r="F189" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G189" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J189" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K189" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="L189" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O189" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="P189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q189" s="2"/>
-      <c r="R189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AG189" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH189" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ189" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL189" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AM189" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AN189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO189" t="s" s="2">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="190" hidden="true">
-      <c r="A190" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="C190" s="2"/>
-      <c r="D190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E190" s="2"/>
-      <c r="F190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G190" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K190" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L190" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="P190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q190" s="2"/>
-      <c r="R190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X190" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="Z190" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AG190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH190" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI190" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AJ190" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM190" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AN190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO190" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="191" hidden="true">
-      <c r="A191" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C191" s="2"/>
-      <c r="D191" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G191" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K191" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L191" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="P191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q191" s="2"/>
-      <c r="R191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X191" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="Z191" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AG191" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH191" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL191" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AM191" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AN191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO191" t="s" s="2">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="192" hidden="true">
-      <c r="A192" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="C192" s="2"/>
-      <c r="D192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L192" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="P192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q192" s="2"/>
-      <c r="R192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ192" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO192" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO192">
+  <autoFilter ref="A1:AO157">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -25168,7 +20937,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI191">
+  <conditionalFormatting sqref="A2:AI156">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
